--- a/samples/L_科目余额表.xlsx
+++ b/samples/L_科目余额表.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -508,19 +508,19 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>720000</v>
+        <v>850000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>8500000</v>
+        <v>12500000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>8630000</v>
+        <v>12800000</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>850000</v>
+        <v>350000</v>
       </c>
     </row>
     <row r="3">
@@ -538,19 +538,19 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6000000</v>
+        <v>9800000</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6100000</v>
+        <v>10000000</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>600000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="4">
@@ -568,19 +568,19 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>120000</v>
+        <v>150000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1440000</v>
+        <v>1800000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1460000</v>
+        <v>1850000</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>140000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="5">
@@ -598,19 +598,49 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>100000</v>
+        <v>80000</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1060000</v>
+        <v>900000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1070000</v>
+        <v>900000</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>110000</v>
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>221104</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>应付职工薪酬-年终奖</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>70000</v>
       </c>
     </row>
   </sheetData>
